--- a/LubanTools/DesignerConfigs/Datas/IslandLevel_岛屿等级表.xlsx
+++ b/LubanTools/DesignerConfigs/Datas/IslandLevel_岛屿等级表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -288,7 +288,31 @@
     <t>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;18;19;20;21;22;23</t>
   </si>
   <si>
-    <t>20001;30|20002;50|2;20</t>
+    <t>2;4000</t>
+  </si>
+  <si>
+    <t>2;8900</t>
+  </si>
+  <si>
+    <t>2;18200</t>
+  </si>
+  <si>
+    <t>2;35500</t>
+  </si>
+  <si>
+    <t>2;51700</t>
+  </si>
+  <si>
+    <t>2;79200</t>
+  </si>
+  <si>
+    <t>2;124900</t>
+  </si>
+  <si>
+    <t>2;163400</t>
+  </si>
+  <si>
+    <t>2;226000</t>
   </si>
   <si>
     <t>森林岛屿</t>
@@ -1487,15 +1511,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="19.375" customWidth="1"/>
     <col min="5" max="6" width="27.25" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="50.375" customWidth="1"/>
-    <col min="9" max="9" width="16.125" customWidth="1"/>
+    <col min="7" max="9" width="16.125" customWidth="1"/>
     <col min="10" max="10" width="9.375" customWidth="1"/>
     <col min="11" max="12" width="8.875" customWidth="1"/>
   </cols>
@@ -1704,7 +1726,7 @@
         <v>36</v>
       </c>
       <c r="I6" s="2">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1733,10 +1755,10 @@
         <v>2000</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" s="2">
-        <v>400</v>
+        <v>542</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1765,10 +1787,10 @@
         <v>2000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I8" s="2">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1797,10 +1819,10 @@
         <v>2000</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I9" s="2">
-        <v>400</v>
+        <v>1151</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1829,10 +1851,10 @@
         <v>2000</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2">
-        <v>400</v>
+        <v>1546</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1861,10 +1883,10 @@
         <v>2000</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I11" s="2">
-        <v>400</v>
+        <v>2079</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1893,10 +1915,10 @@
         <v>2000</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I12" s="2">
-        <v>400</v>
+        <v>2244</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -1925,10 +1947,10 @@
         <v>2000</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I13" s="2">
-        <v>400</v>
+        <v>2690</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1957,10 +1979,10 @@
         <v>2000</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I14" s="2">
-        <v>400</v>
+        <v>3287</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1974,7 +1996,7 @@
         <v>102001</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -1989,9 +2011,7 @@
         <v>2000</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="2">
-        <v>400</v>
-      </c>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2">
@@ -2004,7 +2024,7 @@
         <v>102002</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -2022,7 +2042,7 @@
         <v>36</v>
       </c>
       <c r="I16" s="2">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2036,7 +2056,7 @@
         <v>102003</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -2051,10 +2071,10 @@
         <v>2000</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I17" s="2">
-        <v>400</v>
+        <v>542</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2068,7 +2088,7 @@
         <v>102004</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
@@ -2083,10 +2103,10 @@
         <v>2000</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I18" s="2">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -2100,7 +2120,7 @@
         <v>102005</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -2115,10 +2135,10 @@
         <v>2000</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I19" s="2">
-        <v>400</v>
+        <v>1151</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2132,7 +2152,7 @@
         <v>102006</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -2147,10 +2167,10 @@
         <v>2000</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I20" s="2">
-        <v>400</v>
+        <v>1546</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2164,7 +2184,7 @@
         <v>102007</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -2179,10 +2199,10 @@
         <v>2000</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I21" s="2">
-        <v>400</v>
+        <v>2079</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -2196,7 +2216,7 @@
         <v>102008</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -2211,10 +2231,10 @@
         <v>2000</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I22" s="2">
-        <v>400</v>
+        <v>2244</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -2228,7 +2248,7 @@
         <v>102009</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
@@ -2243,10 +2263,10 @@
         <v>2000</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I23" s="2">
-        <v>400</v>
+        <v>2690</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -2260,7 +2280,7 @@
         <v>102010</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -2275,10 +2295,10 @@
         <v>2000</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2">
-        <v>400</v>
+        <v>3287</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2292,7 +2312,7 @@
         <v>103001</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D25" s="2">
         <v>3</v>
@@ -2307,9 +2327,7 @@
         <v>2000</v>
       </c>
       <c r="H25" s="2"/>
-      <c r="I25" s="2">
-        <v>400</v>
-      </c>
+      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2">
@@ -2322,7 +2340,7 @@
         <v>103002</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -2340,7 +2358,7 @@
         <v>36</v>
       </c>
       <c r="I26" s="2">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -2354,7 +2372,7 @@
         <v>103003</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2">
         <v>3</v>
@@ -2369,10 +2387,10 @@
         <v>2000</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I27" s="2">
-        <v>400</v>
+        <v>542</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -2386,7 +2404,7 @@
         <v>103004</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
@@ -2401,10 +2419,10 @@
         <v>2000</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I28" s="2">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -2418,7 +2436,7 @@
         <v>103005</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2433,10 +2451,10 @@
         <v>2000</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I29" s="2">
-        <v>400</v>
+        <v>1151</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -2450,7 +2468,7 @@
         <v>103006</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -2465,10 +2483,10 @@
         <v>2000</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I30" s="2">
-        <v>400</v>
+        <v>1546</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -2482,7 +2500,7 @@
         <v>103007</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2">
         <v>3</v>
@@ -2497,10 +2515,10 @@
         <v>2000</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I31" s="2">
-        <v>400</v>
+        <v>2079</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -2514,7 +2532,7 @@
         <v>103008</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2">
         <v>3</v>
@@ -2529,10 +2547,10 @@
         <v>2000</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I32" s="2">
-        <v>400</v>
+        <v>2244</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -2546,7 +2564,7 @@
         <v>103009</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
@@ -2561,10 +2579,10 @@
         <v>2000</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I33" s="2">
-        <v>400</v>
+        <v>2690</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -2578,7 +2596,7 @@
         <v>103010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2">
         <v>3</v>
@@ -2593,10 +2611,10 @@
         <v>2000</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I34" s="2">
-        <v>400</v>
+        <v>3287</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -2610,13 +2628,13 @@
         <v>104001</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2">
         <v>4</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
@@ -2625,9 +2643,7 @@
         <v>2000</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="2">
-        <v>400</v>
-      </c>
+      <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2">
@@ -2640,13 +2656,13 @@
         <v>104002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D36" s="2">
         <v>4</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
@@ -2658,7 +2674,7 @@
         <v>36</v>
       </c>
       <c r="I36" s="2">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -2672,13 +2688,13 @@
         <v>104003</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D37" s="2">
         <v>4</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F37" s="4">
         <v>0</v>
@@ -2687,10 +2703,10 @@
         <v>2000</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I37" s="2">
-        <v>400</v>
+        <v>542</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2704,13 +2720,13 @@
         <v>104004</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D38" s="2">
         <v>4</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F38" s="4">
         <v>0</v>
@@ -2719,10 +2735,10 @@
         <v>2000</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I38" s="2">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -2736,13 +2752,13 @@
         <v>104005</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D39" s="2">
         <v>4</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F39" s="4">
         <v>0</v>
@@ -2751,10 +2767,10 @@
         <v>2000</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I39" s="2">
-        <v>400</v>
+        <v>1151</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -2768,13 +2784,13 @@
         <v>104006</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D40" s="2">
         <v>4</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F40" s="4">
         <v>0</v>
@@ -2783,10 +2799,10 @@
         <v>2000</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I40" s="2">
-        <v>400</v>
+        <v>1546</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -2800,13 +2816,13 @@
         <v>104007</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D41" s="2">
         <v>4</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F41" s="4">
         <v>0</v>
@@ -2815,10 +2831,10 @@
         <v>2000</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I41" s="2">
-        <v>400</v>
+        <v>2079</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -2832,13 +2848,13 @@
         <v>104008</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2">
         <v>4</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F42" s="4">
         <v>0</v>
@@ -2847,10 +2863,10 @@
         <v>2000</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I42" s="2">
-        <v>400</v>
+        <v>2244</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2863,13 +2879,13 @@
         <v>104009</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D43" s="2">
         <v>4</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F43" s="4">
         <v>0</v>
@@ -2878,10 +2894,10 @@
         <v>2000</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I43" s="2">
-        <v>400</v>
+        <v>2690</v>
       </c>
       <c r="L43" s="2">
         <v>4</v>
@@ -2892,13 +2908,13 @@
         <v>104010</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D44" s="2">
         <v>4</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F44" s="4">
         <v>0</v>
@@ -2907,10 +2923,10 @@
         <v>2000</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I44" s="2">
-        <v>400</v>
+        <v>3287</v>
       </c>
       <c r="L44" s="2">
         <v>4</v>
